--- a/frontend/public/gen-sticker-docs/originals/08-database.xlsx
+++ b/frontend/public/gen-sticker-docs/originals/08-database.xlsx
@@ -2,20 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual ERD" sheetId="1" r:id="R89f5632483244aa9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual RLS" sheetId="2" r:id="Rb547a460d9cd44b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Lifecycle" sheetId="3" r:id="R82f7b7a64c714167"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" r:id="Re09aab71aee64325"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sticker_packs" sheetId="5" r:id="Rfa8eb4f214e8402a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stickers" sheetId="6" r:id="R4f9b6ac794b54106"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership &amp; RLS" sheetId="7" r:id="R4c128f3be2c04cae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration 001" sheetId="8" r:id="Rdf0f7cc40f4d4c7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage &amp; Gaps" sheetId="9" r:id="Ree0e788af214435c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Model Summary" sheetId="10" r:id="R6462a855fe3445c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="11" r:id="Rf6f3b992a26e4fef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RLS Target" sheetId="12" r:id="Rbf12d932ae2b4070"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage Objects" sheetId="13" r:id="R72639f659d1244b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retention &amp; Deletion" sheetId="14" r:id="Rc2466426e8d846c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual ERD" sheetId="1" r:id="Rcfe4f8a5c43547d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual RLS" sheetId="2" r:id="R8c23eeddd70c4f27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Lifecycle" sheetId="3" r:id="R603df2d324374f55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" r:id="R4566c58f12cc4cae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sticker_packs" sheetId="5" r:id="R2e91866cc3664c45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stickers" sheetId="6" r:id="R75ced49eb94641f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership &amp; RLS" sheetId="7" r:id="Rd7769435cf0b4ea4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration 001" sheetId="8" r:id="R29b1da16841c43f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage &amp; Gaps" sheetId="9" r:id="R48fd6fa3388b4d62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Model Summary" sheetId="10" r:id="R490997619e0a4e08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="11" r:id="R5e0bf9d8eb5049b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RLS Target" sheetId="12" r:id="R18fc0731e4ac413b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage Objects" sheetId="13" r:id="Rc6a505172f78411c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retention &amp; Deletion" sheetId="14" r:id="Rd4136e9e9ee34ba1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Face Gate Data Impact" sheetId="15" r:id="R4992cfddfbde43f8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -500,13 +501,13 @@
     <xdr:ext cx="11734800" cy="6600825"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="40dde49d-9a06-46c7-a7d0-c6ae0b246034"/>
+        <xdr:cNvPr id="1" name="d1391d14-73be-41c1-9ef3-0151eb8d8bc0"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R67b0d9dcecfb4ea6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5c6639645c2c457b"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -532,13 +533,13 @@
     <xdr:ext cx="11734800" cy="6600825"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="281a5a89-7714-4412-95a3-4505ac381997"/>
+        <xdr:cNvPr id="1" name="9f91a7c3-2b6d-4e93-a6b7-d24247c52749"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R9150938f7e0c46f0"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re015e6df8f714db7"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -564,13 +565,13 @@
     <xdr:ext cx="11734800" cy="6600825"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="358b34bf-fa3a-4455-9381-f6c19afc2c7e"/>
+        <xdr:cNvPr id="1" name="0f401170-6971-4a65-901e-39b50b4fc579"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb764db9321a245cc"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R709f5bcc390a4ed0"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -620,6 +621,20 @@
     <x:tableColumn id="3" name="Required SLA"/>
     <x:tableColumn id="4" name="Implementation task"/>
     <x:tableColumn id="5" name="Verification"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="GS0812Table" displayName="GS0812Table" ref="A6:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:E11"/>
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="Condition"/>
+    <x:tableColumn id="2" name="Client state"/>
+    <x:tableColumn id="3" name="Server/storage impact"/>
+    <x:tableColumn id="4" name="Privacy meaning"/>
+    <x:tableColumn id="5" name="Residual gap"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1329,7 +1344,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="51" t="str">
-        <x:v>Nguồn: backend/app/services/supabase_service.py; backend/migrations/001_add_sticker_pack_soft_delete.sql; frontend/src/services/stickerService.ts  •  kien_v5 @ c09e26a  •  2026-08-09</x:v>
+        <x:v>Nguồn: backend/app/services/supabase_service.py; backend/migrations/001_add_sticker_pack_soft_delete.sql; frontend/src/services/stickerService.ts  •  kien_v5 @ 4d23b9a  •  2026-08-10</x:v>
       </x:c>
       <x:c r="B46" s="51"/>
       <x:c r="C46" s="51"/>
@@ -1364,7 +1379,7 @@
   <x:printOptions horizontalCentered="1"/>
   <x:pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6283a1cf41734708"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fa92dd8fba741b1"/>
 </x:worksheet>
 </file>
 
@@ -1399,7 +1414,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-08  •  kien_v5 @ c09e26a  •  2026-08-09  •  Inferred; incomplete migrations</x:v>
+        <x:v>GS-DOC-08  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Inferred; incomplete migrations</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1526,7 +1541,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1194b9a7755a4fdb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f93022d4174440e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1565,7 +1580,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-08  •  kien_v5 @ c09e26a  •  2026-08-09  •  Inferred; incomplete migrations</x:v>
+        <x:v>GS-DOC-08  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Inferred; incomplete migrations</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1692,7 +1707,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa79e96e6cf44d69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c10e871d88f4c39"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1728,7 +1743,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-08  •  kien_v5 @ c09e26a  •  2026-08-09  •  Inferred; incomplete migrations</x:v>
+        <x:v>GS-DOC-08  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Inferred; incomplete migrations</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1855,7 +1870,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27570446f71a4724"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fb93c5a92514334"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1891,7 +1906,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-08  •  kien_v5 @ c09e26a  •  2026-08-09  •  Inferred; incomplete migrations</x:v>
+        <x:v>GS-DOC-08  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Inferred; incomplete migrations</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2001,7 +2016,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b78da9f265b4e58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ec5214a4599414d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2037,7 +2052,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-08  •  kien_v5 @ c09e26a  •  2026-08-09  •  Inferred; incomplete migrations</x:v>
+        <x:v>GS-DOC-08  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Inferred; incomplete migrations</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2164,7 +2179,170 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3068ed65b8348ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65c45e1d6afd4173"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="38" customHeight="1">
+      <x:c r="A1" s="53" t="str">
+        <x:v>08  /  Database Schema &amp; RLS</x:v>
+      </x:c>
+      <x:c r="B1" s="53"/>
+      <x:c r="C1" s="53"/>
+      <x:c r="D1" s="53"/>
+      <x:c r="E1" s="53"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="56" t="str">
+        <x:v>Ảnh reject không đi tới dữ liệu server qua UI chính; accepted/direct API lifecycle giữ nguyên</x:v>
+      </x:c>
+      <x:c r="B2" s="56"/>
+      <x:c r="C2" s="56"/>
+      <x:c r="D2" s="56"/>
+      <x:c r="E2" s="56"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="57" t="str">
+        <x:v>GS-DOC-08  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Inferred; incomplete migrations</x:v>
+      </x:c>
+      <x:c r="B3" s="57"/>
+      <x:c r="C3" s="57"/>
+      <x:c r="D3" s="57"/>
+      <x:c r="E3" s="57"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="58" t="str">
+        <x:v>AS-BUILT • Nội dung viết từ source hiện tại; bộ mẫu chỉ cung cấp cấu trúc trình bày.</x:v>
+      </x:c>
+      <x:c r="B4" s="58"/>
+      <x:c r="C4" s="58"/>
+      <x:c r="D4" s="58"/>
+      <x:c r="E4" s="58"/>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="64" t="str">
+        <x:v>Condition</x:v>
+      </x:c>
+      <x:c r="B6" s="64" t="str">
+        <x:v>Client state</x:v>
+      </x:c>
+      <x:c r="C6" s="64" t="str">
+        <x:v>Server/storage impact</x:v>
+      </x:c>
+      <x:c r="D6" s="64" t="str">
+        <x:v>Privacy meaning</x:v>
+      </x:c>
+      <x:c r="E6" s="64" t="str">
+        <x:v>Residual gap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A7" s="69" t="str">
+        <x:v>0 face</x:v>
+      </x:c>
+      <x:c r="B7" s="69" t="str">
+        <x:v>Rejected local</x:v>
+      </x:c>
+      <x:c r="C7" s="69" t="str">
+        <x:v>No standard-UI upload/job</x:v>
+      </x:c>
+      <x:c r="D7" s="69" t="str">
+        <x:v>Ảnh ở thiết bị</x:v>
+      </x:c>
+      <x:c r="E7" s="69" t="str">
+        <x:v>Direct API bypass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A8" s="70" t="str">
+        <x:v>&gt;1 face</x:v>
+      </x:c>
+      <x:c r="B8" s="70" t="str">
+        <x:v>Rejected local</x:v>
+      </x:c>
+      <x:c r="C8" s="70" t="str">
+        <x:v>No standard-UI upload/job</x:v>
+      </x:c>
+      <x:c r="D8" s="70" t="str">
+        <x:v>Ảnh ở thiết bị</x:v>
+      </x:c>
+      <x:c r="E8" s="70" t="str">
+        <x:v>False count possible</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A9" s="69" t="str">
+        <x:v>1 face verified, not generated</x:v>
+      </x:c>
+      <x:c r="B9" s="69" t="str">
+        <x:v>Preview local</x:v>
+      </x:c>
+      <x:c r="C9" s="69" t="str">
+        <x:v>No upload yet</x:v>
+      </x:c>
+      <x:c r="D9" s="69" t="str">
+        <x:v>Ảnh ở thiết bị</x:v>
+      </x:c>
+      <x:c r="E9" s="69" t="str">
+        <x:v>Browser memory only</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A10" s="70" t="str">
+        <x:v>1 face + Generate</x:v>
+      </x:c>
+      <x:c r="B10" s="70" t="str">
+        <x:v>Generation processing</x:v>
+      </x:c>
+      <x:c r="C10" s="70" t="str">
+        <x:v>Source upload + provider refs</x:v>
+      </x:c>
+      <x:c r="D10" s="70" t="str">
+        <x:v>Existing consent/retention applies</x:v>
+      </x:c>
+      <x:c r="E10" s="70" t="str">
+        <x:v>Public URL/cleanup gaps unchanged</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A11" s="69" t="str">
+        <x:v>Detector failure</x:v>
+      </x:c>
+      <x:c r="B11" s="69" t="str">
+        <x:v>Fail closed</x:v>
+      </x:c>
+      <x:c r="C11" s="69" t="str">
+        <x:v>No standard-UI upload/job</x:v>
+      </x:c>
+      <x:c r="D11" s="69" t="str">
+        <x:v>No external transfer</x:v>
+      </x:c>
+      <x:c r="E11" s="69" t="str">
+        <x:v>CDN/browser availability</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A3:E3"/>
+    <x:mergeCell ref="A4:E4"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3144fe2d10b4af7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2571,7 +2749,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="51" t="str">
-        <x:v>Nguồn: backend/app/security.py; backend/app/services/supabase_service.py; backend/app/database.py  •  kien_v5 @ c09e26a  •  2026-08-09</x:v>
+        <x:v>Nguồn: backend/app/security.py; backend/app/services/supabase_service.py; backend/app/database.py  •  kien_v5 @ 4d23b9a  •  2026-08-10</x:v>
       </x:c>
       <x:c r="B46" s="51"/>
       <x:c r="C46" s="51"/>
@@ -2606,7 +2784,7 @@
   <x:printOptions horizontalCentered="1"/>
   <x:pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ddb93340e26438a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R561093d09b9546c7"/>
 </x:worksheet>
 </file>
 
@@ -2653,7 +2831,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Luồng as-is của selfie, artifact tạm, output và soft delete</x:v>
+        <x:v>Local preflight đứng trước upload từ giao diện; direct API lifecycle giữ nguyên</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -2705,7 +2883,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="16" t="str">
-        <x:v>Năm bước Upload, Generate, Persist, History và Soft delete</x:v>
+        <x:v>Local face gate chạy trước Upload</x:v>
       </x:c>
       <x:c r="B8" s="16"/>
       <x:c r="C8" s="16"/>
@@ -2713,7 +2891,7 @@
       <x:c r="E8" s="16"/>
       <x:c r="F8" s="16"/>
       <x:c r="I8" s="22" t="str">
-        <x:v>ba callout mô tả nguồn selfie, temp artifact và target lifecycle</x:v>
+        <x:v>pass mới gửi backend và Storage, rồi Generate, Persist, History và Soft delete</x:v>
       </x:c>
       <x:c r="J8" s="22"/>
       <x:c r="K8" s="22"/>
@@ -2799,7 +2977,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="28" t="str">
-        <x:v>Vòng đời selfie, temp artifacts, output history và soft delete.</x:v>
+        <x:v>direct API bypass và cleanup Storage vẫn là gap</x:v>
       </x:c>
       <x:c r="B18" s="28"/>
       <x:c r="C18" s="28"/>
@@ -2807,7 +2985,7 @@
       <x:c r="E18" s="28"/>
       <x:c r="F18" s="28"/>
       <x:c r="I18" s="34" t="str">
-        <x:v>Vòng đời selfie, temp artifacts, output history và soft delete.</x:v>
+        <x:v>Vòng đời dữ liệu có bước local preflight trước upload; ảnh reject không đi qua UI tới Storage hay provider.</x:v>
       </x:c>
       <x:c r="J18" s="34"/>
       <x:c r="K18" s="34"/>
@@ -2893,7 +3071,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="43" t="str">
-        <x:v>Luồng as-is của selfie, artifact tạm, output và soft delete
+        <x:v>Local preflight đứng trước upload từ giao diện; direct API lifecycle giữ nguyên
 Implemented  •  Inferred  •  Gap/Risk  •  Recommended</x:v>
       </x:c>
       <x:c r="B28" s="43"/>
@@ -2976,7 +3154,7 @@
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
       <x:c r="A42" s="45" t="str">
-        <x:v>Hình GS-DOC-08 — Vòng đời dữ liệu và điểm giữ lại. Vòng đời selfie, temp artifacts, output history và soft delete.</x:v>
+        <x:v>Hình GS-DOC-08 — Vòng đời dữ liệu và điểm giữ lại. Vòng đời dữ liệu có bước local preflight trước upload; ảnh reject không đi qua UI tới Storage hay provider.</x:v>
       </x:c>
       <x:c r="B42" s="45"/>
       <x:c r="C42" s="45"/>
@@ -2994,7 +3172,7 @@
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
       <x:c r="A44" s="49" t="str">
-        <x:v>Mô tả sơ đồ: Năm bước Upload, Generate, Persist, History và Soft delete; ba callout mô tả nguồn selfie, temp artifact và target lifecycle.</x:v>
+        <x:v>Mô tả sơ đồ: Local face gate chạy trước Upload; pass mới gửi backend và Storage, rồi Generate, Persist, History và Soft delete; direct API bypass và cleanup Storage vẫn là gap.</x:v>
       </x:c>
       <x:c r="B44" s="49"/>
       <x:c r="C44" s="49"/>
@@ -3012,7 +3190,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="51" t="str">
-        <x:v>Nguồn: backend/app/api/stickers.py; backend/app/services/sticker_pipeline.py; backend/app/services/supabase_service.py  •  kien_v5 @ c09e26a  •  2026-08-09</x:v>
+        <x:v>Nguồn: frontend/src/hooks/useImageUpload.ts; backend/app/api/stickers.py; backend/app/services/supabase_service.py  •  kien_v5 @ 4d23b9a  •  2026-08-10</x:v>
       </x:c>
       <x:c r="B46" s="51"/>
       <x:c r="C46" s="51"/>
@@ -3047,7 +3225,7 @@
   <x:printOptions horizontalCentered="1"/>
   <x:pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4ac5ba2af24432a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0104159eab9045c8"/>
 </x:worksheet>
 </file>
 
@@ -3079,7 +3257,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-08  •  kien_v5 @ c09e26a  •  2026-08-09  •  Inferred; incomplete migrations</x:v>
+        <x:v>GS-DOC-08  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Inferred; incomplete migrations</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3200,7 +3378,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R346d16bee3bc4802"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea33790cec5f4c13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3236,7 +3414,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-08  •  kien_v5 @ c09e26a  •  2026-08-09  •  Inferred; incomplete migrations</x:v>
+        <x:v>GS-DOC-08  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Inferred; incomplete migrations</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3414,7 +3592,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re03b79d2ad3f4f07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c94d8cf31244700"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3450,7 +3628,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-08  •  kien_v5 @ c09e26a  •  2026-08-09  •  Inferred; incomplete migrations</x:v>
+        <x:v>GS-DOC-08  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Inferred; incomplete migrations</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3577,7 +3755,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9707afb409348eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04577cc5d3cf4487"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3613,7 +3791,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-08  •  kien_v5 @ c09e26a  •  2026-08-09  •  Inferred; incomplete migrations</x:v>
+        <x:v>GS-DOC-08  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Inferred; incomplete migrations</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3740,7 +3918,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fea4211adf84bdf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e93a015c13746d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3773,7 +3951,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-08  •  kien_v5 @ c09e26a  •  2026-08-09  •  Inferred; incomplete migrations</x:v>
+        <x:v>GS-DOC-08  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Inferred; incomplete migrations</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3866,7 +4044,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R782927431f0a4d54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9dcb1edba1ad4f0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3899,7 +4077,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-08  •  kien_v5 @ c09e26a  •  2026-08-09  •  Inferred; incomplete migrations</x:v>
+        <x:v>GS-DOC-08  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Inferred; incomplete migrations</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -4025,7 +4203,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c4705a3343144ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbad796bb4342448c"/>
   </x:tableParts>
 </x:worksheet>
 </file>